--- a/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/DistriAlunosClasseMT2serie_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/DistriAlunosClasseMT2serie_S3.xlsx
@@ -495,10 +495,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>4109</v>
+        <v>3823</v>
       </c>
       <c r="C10" t="n">
-        <v>13.387</v>
+        <v>12.456</v>
       </c>
     </row>
     <row r="11">
@@ -506,10 +506,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>5831</v>
+        <v>5869</v>
       </c>
       <c r="C11" t="n">
-        <v>18.998</v>
+        <v>19.122</v>
       </c>
     </row>
     <row r="12">
@@ -517,10 +517,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>5209</v>
+        <v>5293</v>
       </c>
       <c r="C12" t="n">
-        <v>16.971</v>
+        <v>17.245</v>
       </c>
     </row>
     <row r="13">
@@ -528,10 +528,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>4525</v>
+        <v>4581</v>
       </c>
       <c r="C13" t="n">
-        <v>14.743</v>
+        <v>14.925</v>
       </c>
     </row>
     <row r="14">
@@ -539,10 +539,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>3763</v>
+        <v>3783</v>
       </c>
       <c r="C14" t="n">
-        <v>12.26</v>
+        <v>12.325</v>
       </c>
     </row>
     <row r="15">
@@ -550,10 +550,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>7256</v>
+        <v>7344</v>
       </c>
       <c r="C15" t="n">
-        <v>23.641</v>
+        <v>23.927</v>
       </c>
     </row>
   </sheetData>
